--- a/StructureDefinition-access-data-reporting-bundle.xlsx
+++ b/StructureDefinition-access-data-reporting-bundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:45:33-04:00</t>
+    <t>2026-05-18T15:59:44-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
-bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}</t>
+bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}access-data-reporting-bundle-composition-refs-in-bundle:All resources referenced from the data reporting Composition must be included in the enclosing data reporting Bundle. {entry.resource.ofType(Composition).descendants().ofType(Reference).all(resolve() in %resource.entry.resource)}</t>
   </si>
   <si>
     <t>N/A</t>
@@ -998,7 +998,7 @@
     <t>Bundle.entry:access-data-reporting-composition.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Composition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-data-reporting-composition|0.9.6}
+    <t xml:space="preserve">Composition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-data-reporting-composition|0.9.8}
 </t>
   </si>
   <si>

--- a/StructureDefinition-access-data-reporting-bundle.xlsx
+++ b/StructureDefinition-access-data-reporting-bundle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T15:59:44-04:00</t>
+    <t>2026-05-20T09:30:43-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-access-data-reporting-bundle.xlsx
+++ b/StructureDefinition-access-data-reporting-bundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.8</t>
+    <t>0.9.11</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-20T09:30:43-04:00</t>
+    <t>2026-06-04T22:54:52-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -998,7 +998,7 @@
     <t>Bundle.entry:access-data-reporting-composition.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Composition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-data-reporting-composition|0.9.8}
+    <t xml:space="preserve">Composition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-data-reporting-composition|0.9.11}
 </t>
   </si>
   <si>
@@ -1438,7 +1438,7 @@
     <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="96.65625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="97.65625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-access-data-reporting-bundle.xlsx
+++ b/StructureDefinition-access-data-reporting-bundle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T22:54:52-04:00</t>
+    <t>2026-06-04T23:05:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-access-data-reporting-bundle.xlsx
+++ b/StructureDefinition-access-data-reporting-bundle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.11</t>
+    <t>0.9.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T23:05:21-04:00</t>
+    <t>2026-06-10T23:08:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -998,7 +998,7 @@
     <t>Bundle.entry:access-data-reporting-composition.resource</t>
   </si>
   <si>
-    <t xml:space="preserve">Composition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-data-reporting-composition|0.9.11}
+    <t xml:space="preserve">Composition {https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-data-reporting-composition|0.9.12}
 </t>
   </si>
   <si>
